--- a/results/optA_20251016_200330/consolidated_analysis/cross_dataset_comparison/detection_performance_all_datasets.xlsx
+++ b/results/optA_20251016_200330/consolidated_analysis/cross_dataset_comparison/detection_performance_all_datasets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Best Epoch</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>mAP@50</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mAP@50-95</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
@@ -480,16 +485,19 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9381</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7771</v>
+        <v>0.9606</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9022</v>
+        <v>0.7843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9222</v>
+        <v>0.913</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9331</v>
       </c>
     </row>
     <row r="3">
@@ -507,16 +515,19 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9499</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7776</v>
+        <v>0.9638</v>
       </c>
       <c r="F3" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.9191</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.9111</v>
+      <c r="H3" t="n">
+        <v>0.9333</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +545,19 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0.944</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7821</v>
+        <v>0.9647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.922</v>
+        <v>0.6734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8667</v>
+        <v>0.8902</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8889</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +575,19 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7084</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5705</v>
+        <v>0.7469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.5908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7105</v>
+        <v>0.6838</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7039</v>
       </c>
     </row>
     <row r="6">
@@ -588,16 +605,19 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7291</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.7491</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6858</v>
+        <v>0.5482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.757</v>
+        <v>0.61</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7726</v>
       </c>
     </row>
     <row r="7">
@@ -615,16 +635,19 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7112000000000001</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5693</v>
+        <v>0.7459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6592</v>
+        <v>0.5356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7518</v>
+        <v>0.625</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7778</v>
       </c>
     </row>
     <row r="8">
@@ -642,16 +665,19 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9244</v>
+        <v>93</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6012</v>
+        <v>0.9277</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8567</v>
+        <v>0.5934</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9073</v>
+        <v>0.8612</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8985</v>
       </c>
     </row>
     <row r="9">
@@ -669,16 +695,19 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9257</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6217</v>
+        <v>0.9324</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8652</v>
+        <v>0.6108</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9188</v>
+        <v>0.8904</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8945</v>
       </c>
     </row>
     <row r="10">
@@ -696,16 +725,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9272</v>
+        <v>89</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.9366</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8899</v>
+        <v>0.6229</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8928</v>
+        <v>0.885</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9073</v>
       </c>
     </row>
     <row r="11">
@@ -723,16 +755,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9378</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4448</v>
+        <v>0.96</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9157</v>
+        <v>0.5493</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9312</v>
+        <v>0.95</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9049</v>
       </c>
     </row>
     <row r="12">
@@ -750,16 +785,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9448</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6034</v>
+        <v>0.9559</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9315</v>
+        <v>0.5143</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.9324</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8889</v>
       </c>
     </row>
     <row r="13">
@@ -777,15 +815,18 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9627</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.6153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.9291</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.9258999999999999</v>
       </c>
     </row>
